--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>Senior Database Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Linqd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb5a838303cab7f</t>
+          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>Techneaux Technology Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>Lafayette, LA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior, Agentic AI Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2002a3bb054db4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae15109dd782046</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=771ada6d7a170a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer / Cloud Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Keystone Sports Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenixville, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=affa4e6360039969</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java, Data, Enterprise Platforms &amp; Systems Integration) *HYBRID*</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db9971acfda0ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wells, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solution Architect (Remote)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SymphonyAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f39d74ff9af060</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3088413e5cc3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Forward Deployed</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,54 +3086,54 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064413364274663f</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51aff6d75298585b</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=effa4b02999ec16e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9f5aa1271db099</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior IT Analyst Applications</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,42 +3436,42 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
@@ -3483,55 +3483,55 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9018400b489f06</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e6001b0478b70</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Programmer ETL Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402919188bfdae39</t>
+          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Customer Success Architect</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, ETL, dbt, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953ecd5971ae2bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d9d25071f99932</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1813e12093c4b179</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,49 +3821,49 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73073c20113d8a46</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af75c8c96d0f7286</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed579d893abdf468</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629b5423aca4370</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5e37dc37d36afe</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wells, ME, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ac85c48b014a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Migration</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc849c83d3469f7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data and Solutions Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SitelogIQ</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Security Automation Engineer, 18-month Term</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>UChicago Medicine AdventHealth</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f9e4f52b5f7087</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Full Stack Senior Java Developer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Attadale Partners, LLC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
+          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Solution Architect - Applications &amp; Cloud</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>LSB Industries</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
+          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
+          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
+          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
+          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Fortegra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Managing Engineer , Database &amp; Platform - Remote</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, MongoDB, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,2702 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d30f4ab12fb26c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28d9d25071f99932</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed579d893abdf468</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1813e12093c4b179</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c629b5423aca4370</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de5e37dc37d36afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73073c20113d8a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af75c8c96d0f7286</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41ac85c48b014a3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SAS Developer (with Admin Background)</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Senior Data and Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SitelogIQ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Fortegra</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,42 +573,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
+          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,11 +618,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Database Analyst</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Linqd</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Database Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Linqd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
+          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Techneaux Technology Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
+          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Techneaux Technology Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lafayette, LA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,54 +2771,54 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PostgreSQL Database Administrator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>DrFirst</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=90f5afd899e8dd0f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior, Agentic AI Engineer</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,77 +3531,77 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Programmer ETL Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Programmer ETL Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wells, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Wells, ME, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Security Automation Engineer, 18-month Term</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>UChicago Medicine AdventHealth</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>IAM, RDS, Azure, Databricks, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f9e4f52b5f7087</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Security Automation Engineer, 18-month Term</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UChicago Medicine AdventHealth</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f9e4f52b5f7087</t>
+          <t>https://www.indeed.com/viewjob?jk=4de630e39f231f22</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5374b0f8b1e51540</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>CommunityAmerica Credit Union</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e91167fb94b36fc</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=4949636e6e78aeb4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,29 +4896,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Blackfoot Telephone Cooperative</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,59 +5221,59 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full Stack Senior Java Developer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Attadale Partners, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Solution Architect - Applications &amp; Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LSB Industries</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Web Application Architect 4 (INDG)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
+          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Full Stack Senior Java Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Attadale Partners, LLC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Solution Architect - Applications &amp; Cloud</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LSB Industries</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
+          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
+          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
+          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
+          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
+          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
+          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
+          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
+          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d9d25071f99932</t>
+          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed579d893abdf468</t>
+          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1813e12093c4b179</t>
+          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629b5423aca4370</t>
+          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5e37dc37d36afe</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73073c20113d8a46</t>
+          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af75c8c96d0f7286</t>
+          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ac85c48b014a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
@@ -6838,17 +6838,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Senior Data and Solutions Engineer</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SitelogIQ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,40 +8196,75 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>Senior Data and Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SitelogIQ</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
           <t>Senior Data Analyst</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Fortegra</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
+      <c r="D224" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E224" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
         </is>

--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Database Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Linqd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Database Analyst</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Linqd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
+          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Techneaux Technology Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lafayette, LA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
+          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Techneaux Technology Services</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>PostgreSQL Database Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>DrFirst</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,69 +2761,69 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=90f5afd899e8dd0f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PostgreSQL Database Administrator</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DrFirst</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f5afd899e8dd0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior, Agentic AI Engineer</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>Data Programmer ETL Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,137 +3506,137 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Programmer ETL Data Engineer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=4de630e39f231f22</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wells, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5374b0f8b1e51540</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Security Automation Engineer, 18-month Term</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>UChicago Medicine AdventHealth</t>
+          <t>CommunityAmerica Credit Union</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f9e4f52b5f7087</t>
+          <t>https://www.indeed.com/viewjob?jk=0e91167fb94b36fc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de630e39f231f22</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=4949636e6e78aeb4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Analytics Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5374b0f8b1e51540</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CommunityAmerica Credit Union</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e91167fb94b36fc</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4949636e6e78aeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,207 +5046,207 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Web Application Architect 4 (INDG)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Full Stack Senior Java Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Attadale Partners, LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solution Architect - Applications &amp; Cloud</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>LSB Industries</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Blackfoot Telephone Cooperative</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Web Application Architect 4 (INDG)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
+          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full Stack Senior Java Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Attadale Partners, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
+          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Solution Architect - Applications &amp; Cloud</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LSB Industries</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
+          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
+          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
+          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
+          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
+          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
+          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
+          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
+          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
+          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Applications Engineer - Engineering</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Applications Engineer - General</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
+          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,24 +7881,24 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Data and Solutions Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>SitelogIQ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,357 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Senior Data and Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>SitelogIQ</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Fortegra</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Senior Cloud Engineer - AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
+          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Techneaux Technology Services</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
+          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Techneaux Technology Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lafayette, LA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PostgreSQL Database Administrator</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DrFirst</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f5afd899e8dd0f</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Programmer ETL Data Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Data Architect - Iselin, NJ (Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Summit, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de630e39f231f22</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Japan Communications, inc - US</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f30af03c6caacb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Analytics Data Scientist</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5374b0f8b1e51540</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CommunityAmerica Credit Union</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e91167fb94b36fc</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
@@ -4463,55 +4463,55 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4949636e6e78aeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,102 +4556,102 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,172 +4661,172 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Web Application Architect 4 (INDG)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
+          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Solution Architect - Applications &amp; Cloud</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>LSB Industries</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Blackfoot Telephone Cooperative</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Web Application Architect 4 (INDG)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
+          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full Stack Senior Java Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Attadale Partners, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, Oracle, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2519325a56ffef70</t>
+          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Solution Architect - Applications &amp; Cloud</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LSB Industries</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
+          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
+          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
+          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
+          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
+          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
+          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
+          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
+          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
+          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
+          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
+          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
+          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Applications Engineer - Engineering</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Applications Engineer - General</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Data and Solutions Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>SitelogIQ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7425,496 +7425,6 @@
         </is>
       </c>
       <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Senior Data and Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>SitelogIQ</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
         </is>

--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - AWS</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>28.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Redshift, ECS, Azure, GCP, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
+          <t>https://www.indeed.com/viewjob?jk=62f2ea4b9227ad1a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f021406866c8cb1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Redshift, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Oozie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
+          <t>https://www.indeed.com/viewjob?jk=e788b64bde37944b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Engineer - AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
+          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>24.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff822c60b8aee53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>24.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, ECS, RDS, Azure, Databricks, GCP, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
+          <t>https://www.indeed.com/viewjob?jk=28b17aa00b0fc706</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Senior AI Engineer- Application Development</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=399227e084d1df1f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Database Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Linqd</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
+          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Techneaux Technology Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>Senior Database Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Linqd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Techneaux Technology Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lafayette, LA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Hadoop, HDFS, Hive, Sqoop, Impala, Spark, PySpark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f4fcf4bdf627b93</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior, Agentic AI Engineer</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,242 +3016,242 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,207 +3366,207 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect - Iselin, NJ (Hybrid)</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Summit, NJ, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>Senior Data Architect – R01565908</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ac7aba73aa7703</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
+          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,81 +3597,81 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>gWorks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c782aadc2047f1e8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,242 +3716,242 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=6749ff86086e830c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=496e400decbd9200</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect - Iselin, NJ (Hybrid)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Summit, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,52 +4091,52 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
@@ -4148,20 +4148,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
@@ -4218,82 +4218,82 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Integrity Marketing Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad459674cc4aabaf</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Japan Communications, inc - US</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f30af03c6caacb</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
+          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,172 +4416,172 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud DevOps Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>Scala, MongoDB, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=3b704942f95cf9c7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Blackfoot Telephone Cooperative</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4eee9f0ea41c7fa6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=69e79b06997ed521</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, Kafka, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=26a734af59193b4d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Service Now Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c738d13d9e81f79f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,59 +4661,59 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Web Application Architect 4 (INDG)</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eeacc3f75acc9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde0876b01f2068e</t>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Solution Architect - Applications &amp; Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LSB Industries</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
+          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Web Application Architect 4 (INDG)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
+          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Solution Architect - Applications &amp; Cloud</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LSB Industries</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835bda95513a3d85</t>
+          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dc7c415d19100df</t>
+          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103fe3333c991254</t>
+          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554d9ce02a41efeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7213ce2aafb555d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba0eb498ddcf001</t>
+          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5726e1ce23559cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5260e3b79fcd48</t>
+          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f639f656255cdfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b4d168a9aa4c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b96fb05120de77</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949184fd246efc40</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c3eeec59cb3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aca5d41f260c85b</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b291eed1c513462f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a72baf55f9ff3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9285549c4bca1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750a47fb648633d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46e79152e83532</t>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767a284e6cca4140</t>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbed2bdff5fcf37c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Applications Engineer - General</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Applications Engineer - Engineering</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487fab5c6f99bdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=236bdbba9a2662be</t>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>SAS Developer (with Admin Background)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Senior Data and Solutions Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>SitelogIQ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Python Developer (Linux exp)</t>
+          <t>Junior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,507 +6926,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Senior Data and Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SitelogIQ</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a73266d2d7d833b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-28.xlsx
+++ b/results/job_matches_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Database Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Linqd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Database Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Linqd</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
+          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Techneaux Technology Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa775b4df0e782</t>
+          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Cyber Full-Stack Developer/Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Hadoop, HDFS, Hive, Sqoop, Impala, Spark, PySpark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f4fcf4bdf627b93</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,54 +2876,54 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, Sqoop, Impala, Spark, PySpark, Scala, Kafka, MySQL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f4fcf4bdf627b93</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Insights</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior, Agentic AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,112 +3321,112 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49edbeaf629e68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Back End Developer</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>Sr. AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>Senior Data Architect – R01565908</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,77 +3461,77 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ac7aba73aa7703</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Product</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Architect – R01565908</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>gWorks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ac7aba73aa7703</t>
+          <t>https://www.indeed.com/viewjob?jk=c782aadc2047f1e8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Data Programmer ETL Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f29250114817e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbbc6f44179a3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gWorks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c782aadc2047f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=496e400decbd9200</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Engineer &amp; Workflow Automation Specialist</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3931a67eb51851c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
+          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6749ff86086e830c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Data Architect - Iselin, NJ (Hybrid)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Summit, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e400decbd9200</t>
+          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,42 +3846,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,129 +3891,129 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Architect - Iselin, NJ (Hybrid)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Summit, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
+          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Full-Stack Engineer – Platform Systems (Backend)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Terzo Enterprises</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=016bba447faebcb6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,89 +4136,89 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer Intern</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>Diagonal Matrix Ltd</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=47d2b2ec898613d9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Integrity Marketing Group</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad459674cc4aabaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dallas College</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cloud DevOps Developer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Scala, MongoDB, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b704942f95cf9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eee9f0ea41c7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=0733724faed40ddd</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4598,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>Junior Data Platform Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>MERS Missouri Goodwill Industries</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
+          <t>https://www.indeed.com/viewjob?jk=50a28e98864b0c14</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,67 +4696,67 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Cloud DevOps Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>Scala, MongoDB, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+          <t>https://www.indeed.com/viewjob?jk=3b704942f95cf9c7</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Blackfoot Telephone Cooperative</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
+          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blackfoot Telephone Cooperative</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a29d0256393717</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Web Application Architect 4 (INDG)</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Data Architect (LOC)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, RDS, Azure, Scala, Oracle</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8355770dcb1b03</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5553ffefe7bc8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Solution Architect - Applications &amp; Cloud</t>
+          <t>Web Application Architect 4 (INDG)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LSB Industries</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8008bf1ed943866c</t>
+          <t>https://www.indeed.com/viewjob?jk=af35e473b5aa0bae</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d203c0ff61d232d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccd38d8e3aeaa20</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>R&amp;T Software Engineer 3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Safan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6039c0cbe7afd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3e2857ffc20efe</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9000febff9daed1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929a8e5132072847</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7773ac1a9f155496</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d892306f314dfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5826adebcdccc48</t>
+          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dd0f8cecd4b5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bee803e4f0dcd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a6c8e307c8c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e5d2d10b77d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Applications Engineer - General</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Applications Engineer - Engineering</t>
+          <t>Python Developer (Linux exp)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
+          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2aac28dcc0f5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4146e405f3fbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bca136c0cbbd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb82cab981d6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a98dbf9c8fe27</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b093881e17977137</t>
+          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4dbb9ab25a3de63</t>
+          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9f24b67c3c4865</t>
+          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef59adf435c5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d24847f11cdb17f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d395603d3ca5ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74adefa45fe68b85</t>
+          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf2b3f58c12d5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd4b711a07ed63</t>
+          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4869f36c77523299</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f7505979d19749</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578382c88fd086a2</t>
+          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef8f4a759ab87ae</t>
+          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbf49b5212a6ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d436aca8295c586b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b4244a09c34f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6439cfee5536bdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d582eb6aeb90686e</t>
+          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0f36a33d79abf4</t>
+          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4268b4592450d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76575c65289cbf84</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,427 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c8a8ca939a0761</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df067d3d6da3e98c</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7003b52e283536</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e3e0a28ae521e</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ed7ccbe8bd31d</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77e00ed279d54c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54f346d2d047be10</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e597bdb9ca96785</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd439e16cc7656e</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Python Developer (Linux exp)</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fc23afb90236d1db</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>SAS Developer (with Admin Background)</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Senior Data and Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SitelogIQ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Junior DevOps Engineer, AI Platform</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a73266d2d7d833b4</t>
         </is>
       </c>
     </row>
